--- a/metrics/Metrics_Ablation_Study_RHm_DT.xlsx
+++ b/metrics/Metrics_Ablation_Study_RHm_DT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.283896070547338</v>
+        <v>2.229082435726583</v>
       </c>
       <c r="C2" t="n">
-        <v>2.305006140030803</v>
+        <v>2.173433970797867</v>
       </c>
       <c r="D2" t="n">
-        <v>7.029296900815682</v>
+        <v>6.619243185321924</v>
       </c>
       <c r="E2" t="n">
-        <v>2.651282123957328</v>
+        <v>2.572788989661205</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9118382832651932</v>
+        <v>0.925654544421286</v>
       </c>
       <c r="G2" t="n">
-        <v>0.955076402134532</v>
+        <v>0.9625420329119239</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9560816188521616</v>
+        <v>0.9627957503732144</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8234774753494269</v>
+        <v>0.8422107331167471</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008337630353265124</v>
+        <v>2.452371072055084</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1044266329081176</v>
+        <v>2.759978036448248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4785517339628408</v>
+        <v>7.403616286272614</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4795927876690895</v>
+        <v>2.720958707197266</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4086284264130014</v>
+        <v>0.9204601388968958</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1156660362615511</v>
+        <v>0.9735603187994728</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1513345610364072</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9778488720075841</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8935936146258626</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.259048026536276</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.200909329554903</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.127552521656618</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.475389367686752</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9172806259380751</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9581182594172097</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9503883300193995</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8144822392647418</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.130055803191442</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.849196100107092</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>6.626592865834916</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.574216942263203</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.921123662305765</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.9658794939906097</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9654004261618367</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8499729203852248</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.01231929529380804</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1504719189705699</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.006619800549274524</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.008274028579857429</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.01675178925276383</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1524704586319177</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.1557351073930642</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3417325565808078</v>
+        <v>0.3628209106183312</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2026672455977016</v>
+        <v>0.2337382726408848</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2616492746205308</v>
+        <v>0.2766356660086516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5115166415870854</v>
+        <v>0.5259616583066218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9533369597795952</v>
+        <v>0.9558639167692238</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9780898009751294</v>
+        <v>0.9794325996912577</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9836312571702269</v>
+        <v>0.9826448798963169</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8938296316803452</v>
+        <v>0.8913740680696871</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008087884888169139</v>
+        <v>0.2360895374482541</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04321007193070797</v>
+        <v>0.2202601612462511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4898955613093616</v>
+        <v>0.07870988600120497</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4903364827498725</v>
+        <v>0.2805528221230451</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4431538965731668</v>
+        <v>0.9858807765210109</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03005452771259257</v>
+        <v>0.9937402304617808</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01879688301240771</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9921748942063442</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9395593675425576</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2551802003168382</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.179950870489316</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.13913679417115</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3730104478042807</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9529428616371898</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9858615844097457</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9880299581796659</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.9103206511566067</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.472955716909165</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3271893644700414</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4304261874353272</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6560687368220858</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9381363867896375</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9785026080143027</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9818927566505589</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8935449051465778</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.01169492881286199</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.07021604097206288</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.004545189637124414</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.005782194723670142</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01561050240940015</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.05297562624206062</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.04715997076665573</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.150835293361703</v>
+        <v>1.165300159546344</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5986245140859281</v>
+        <v>0.5813851894207183</v>
       </c>
       <c r="D4" t="n">
-        <v>3.258896095584689</v>
+        <v>3.282348406408996</v>
       </c>
       <c r="E4" t="n">
-        <v>1.80524128458904</v>
+        <v>1.811725256877818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9485392662848179</v>
+        <v>0.9535710549332362</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9740305112575819</v>
+        <v>0.9766632357820535</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9761333269446549</v>
+        <v>0.9752284354573368</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8751467892779508</v>
+        <v>0.8750808493632514</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007961875547774055</v>
+        <v>1.451216170351243</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1455278788811963</v>
+        <v>1.167277724207105</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4886450315421559</v>
+        <v>4.003469603806934</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4854841590322453</v>
+        <v>2.000867212937164</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4326875458675764</v>
+        <v>0.952454484366285</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09697273360687264</v>
+        <v>0.9858855259892789</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05635791527822004</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9849732412747013</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.9182124021262483</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.218202117871048</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.5997751023111227</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.968308341202407</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.992061329678985</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9027442172344341</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9598666990713578</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9532135121735328</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8393758586385409</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.029851849837301</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.5093667830290691</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.611948009792177</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.61615222358297</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9665523500139894</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9858378142418786</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.9818725210249186</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8925721231633422</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01483949916347183</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2757160519645625</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.007324257334862083</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.006603642812613664</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01497064926328823</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.195713859749144</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.1204044507056983</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
